--- a/safety_inspection_forms/023_gym_facility_safety_inspection_consent_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/023_gym_facility_safety_inspection_consent_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Facility Email</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Client Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Facility Inspector Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Client Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Facility Signature</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>facility_inspection_frequency</t>
+          <t>facility_inspection_frequency_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>facility_inspection_frequency_choices</t>
+          <t>facility_inspection_frequency_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>facility_inspection_frequency_choices</t>
+          <t>facility_inspection_frequency_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>facility_inspection_frequency_choices</t>
+          <t>facility_inspection_frequency_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1572,7 +1572,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>facility_inspection_frequency_choices</t>
+          <t>facility_inspection_frequency_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
